--- a/mise_en_donnees_xlsx/mise_en_donnees_materiaux.xlsx
+++ b/mise_en_donnees_xlsx/mise_en_donnees_materiaux.xlsx
@@ -13,9 +13,10 @@
     <sheet name="CPh70" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ZURAM" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="SC-1008" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Liège-phénolique" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Carbone" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Silice" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MX-4926" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Liège-phénolique" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Carbone" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Silice" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
@@ -32,6 +33,8 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000000000000"/>
     <numFmt numFmtId="170" formatCode="0.000000"/>
+    <numFmt numFmtId="171" formatCode="0.00000000"/>
+    <numFmt numFmtId="172" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -175,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -264,6 +267,13 @@
     <xf numFmtId="11" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -635,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
@@ -666,7 +676,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fichier(s) XML : data/mixtures/ — 8 matériaux, 16 fichiers de mélange</t>
+          <t>Fichier(s) XML : data/mixtures/ — 9 matériaux, 17 fichiers de mélange</t>
         </is>
       </c>
     </row>
@@ -873,199 +883,204 @@
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
+          <t>MX-4926</t>
+        </is>
+      </c>
+      <c r="C16" s="8">
+        <f>'MX-4926'!C68</f>
+        <v>0.2526</v>
+      </c>
+      <c r="D16" s="8">
+        <f>'MX-4926'!D68</f>
+        <v>0.6407</v>
+      </c>
+      <c r="E16" s="8">
+        <f>'MX-4926'!E68</f>
+        <v>0.1068</v>
+      </c>
+      <c r="F16" s="9">
+        <f>'MX-4926'!D68/'MX-4926'!E68</f>
+        <v>5.999063670411985</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>C:1.0</t>
+        </is>
+      </c>
+      <c r="H16" s="8">
+        <f>'MX-4926'!C56</f>
+        <v>0.18168390165143375</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
           <t>Liège/phénolique</t>
         </is>
       </c>
-      <c r="C16" s="8">
+      <c r="C17" s="8">
         <f>'Liège-phénolique'!C80</f>
         <v>0.287</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D17" s="8">
         <f>'Liège-phénolique'!D80</f>
         <v>0.592</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E17" s="8">
         <f>'Liège-phénolique'!E80</f>
         <v>0.121</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F17" s="9">
         <f>'Liège-phénolique'!D80/'Liège-phénolique'!E80</f>
         <v>4.892561983471074</v>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>C:1.0</t>
         </is>
       </c>
-      <c r="H16" s="8">
+      <c r="H17" s="8">
         <f>'Liège-phénolique'!C120</f>
         <v>4.0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Carbone graphite</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>C:1.0</t>
         </is>
       </c>
-      <c r="H17" s="8">
+      <c r="H18" s="8">
         <f>'Carbone'!C53</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Silice SiO2</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Si:1.0, O:2.0</t>
         </is>
       </c>
-      <c r="H18" s="8">
+      <c r="H19" s="8">
         <f>'Silice'!C46</f>
         <v>0.0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="12" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Les colonnes « gaz » sont des liens vers la ligne « valeur portée dans le XML » de chaque onglet. Le graphite et la silice n'ont pas de gaz de pyrolyse (k = 0). TACOT et CPh70 portent RIGOUREUSEMENT la même composition : leurs fichiers XML sont identiques, seul k les distingue — c'est la démonstration de l'onglet CPh70.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>§3 — LES TROIS SEULES DONNÉES QUE CONSOMME LE CALCUL</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Composition</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Rôle dans le bilan</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Option</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Comment on l'obtient</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>bord de couche limite</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Y_e</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>-bl</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>l'atmosphère : air N:0.79 O:0.21 · Mars · Titan…</t>
-        </is>
-      </c>
-      <c r="G23" s="15" t="inlineStr"/>
-      <c r="H23" s="15" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>gaz de pyrolyse</t>
+          <t>bord de couche limite</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Y_g</t>
+          <t>Y_e</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>-py</t>
+          <t>-bl</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>c'est TOUT l'objet de ce classeur — quatre routes possibles, §4</t>
+          <t>l'atmosphère : air N:0.79 O:0.21 · Mars · Titan…</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr"/>
@@ -1073,127 +1088,125 @@
     </row>
     <row r="25">
       <c r="B25" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>char</t>
+          <t>gaz de pyrolyse</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Y_c</t>
+          <t>Y_g</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>-char + -char-elem</t>
+          <t>-py</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>C:1.0 si tous les constituants carbonisent vers le carbone ; sinon pondérer par les masses de char</t>
+          <t>c'est TOUT l'objet de ce classeur — quatre routes possibles, §4</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr"/>
       <c r="H25" s="15" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Y_c</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>-char + -char-elem</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>C:1.0 si tous les constituants carbonisent vers le carbone ; sinon pondérer par les masses de char</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr"/>
+      <c r="H26" s="15" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Plus T, P et B'g. Rien d'autre : cf. src/apps/bprime.cpp:304-330. Sans -char/-char-elem, bprime utilise un char de carbone pur intégré ; les deux options vont toujours ensemble.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>§4 — LES QUATRE ROUTES DE CALCUL DU GAZ DE PYROLYSE</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="6" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Matériau</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Donnée primaire</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Passage à l'élémentaire</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Point critique</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A — sommation atomique</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>TACOT, CPh70</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>spéciation moléculaire mesurée (7 espèces)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>n_E = Σ_j ν_E,j · x_j</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>la renormalisation : somme réelle des colonnes (100.30), pas les totaux imprimés (100.0)</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr"/>
-      <c r="H30" s="15" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>B — conversion directe</t>
+          <t>A — sommation atomique</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>ZURAM</t>
+          <t>TACOT, CPh70</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>composition élémentaire MASSIQUE mesurée</t>
+          <t>spéciation moléculaire mesurée (7 espèces)</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>x_E = (y_E/M_E) / Σ (y_j/M_j)</t>
+          <t>n_E = Σ_j ν_E,j · x_j</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>traçabilité limitée à 3 décimales ; la source primaire VKI n'est pas publique</t>
+          <t>la renormalisation : somme réelle des colonnes (100.30), pas les totaux imprimés (100.0)</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr"/>
@@ -1202,27 +1215,27 @@
     <row r="32" ht="28" customHeight="1">
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>C — fermeture élémentaire</t>
+          <t>B — conversion directe</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>SC-1008</t>
+          <t>ZURAM</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>motif chimique idéalisé + rendement en char</t>
+          <t>composition élémentaire MASSIQUE mesurée</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>n_E(gaz) = n_E(résine) − n_E(char)</t>
+          <t>x_E = (y_E/M_E) / Σ (y_j/M_j)</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>le rendement en char entre DANS la chaîne : ±0.05 sur Y déplace le carbone de ~12 %</t>
+          <t>traçabilité limitée à 3 décimales ; la source primaire VKI n'est pas publique</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr"/>
@@ -1231,27 +1244,27 @@
     <row r="33" ht="28" customHeight="1">
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>D — fermeture sur DEUX constituants</t>
+          <t>C — fermeture élémentaire</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Liège/phénolique</t>
+          <t>SC-1008</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>analyses des deux constituants + rendements</t>
+          <t>motif chimique idéalisé + rendement en char</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>n_E(gaz) = Σ_i [n_E(i) − n_E(char,i)]</t>
+          <t>n_E(gaz) = n_E(résine) − n_E(char)</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>le renfort pyrolyse : le rapport renfort/résine entre dans la table B'</t>
+          <t>le rendement en char entre DANS la chaîne : ±0.05 sur Y déplace le carbone de ~12 %</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr"/>
@@ -1260,85 +1273,93 @@
     <row r="34" ht="28" customHeight="1">
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>E — stœchiométrie directe</t>
+          <t>D — fermeture sur DEUX constituants</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>Carbone, Silice</t>
+          <t>Liège/phénolique</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>la formule du solide</t>
+          <t>analyses des deux constituants + rendements</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>aucun gaz de pyrolyse (B'g = 0)</t>
+          <t>n_E(gaz) = Σ_i [n_E(i) − n_E(char,i)]</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>le char EST le matériau ; pour la silice, -char-elem devient Si</t>
+          <t>le renfort pyrolyse : le rapport renfort/résine entre dans la table B'</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>E — stœchiométrie directe</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Carbone, Silice</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>la formule du solide</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>aucun gaz de pyrolyse (B'g = 0)</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>le char EST le matériau ; pour la silice, -char-elem devient Si</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr"/>
+      <c r="H35" s="15" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>§5 — CE QUI N'ENTRE PAS DANS LE XML</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Donnée</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Dans le XML ?</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Où elle sert vraiment</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>masse volumique ρ_v, ρ_c</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>solveur de réponse matériau ; récession ṡ = B'c·ṁe/ρ_c</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr"/>
-      <c r="F38" s="15" t="inlineStr"/>
-      <c r="G38" s="15" t="inlineStr"/>
-      <c r="H38" s="15" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>porosité</t>
+          <t>masse volumique ρ_v, ρ_c</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -1348,7 +1369,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>conduction, perméabilité</t>
+          <t>solveur de réponse matériau ; récession ṡ = B'c·ṁe/ρ_c</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr"/>
@@ -1359,17 +1380,17 @@
     <row r="40">
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>rapport fibres/résine</t>
+          <t>porosité</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>non *</t>
+          <t>non</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>fixe la QUANTITÉ de gaz (donc B'g), pas sa composition</t>
+          <t>conduction, perméabilité</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr"/>
@@ -1380,7 +1401,7 @@
     <row r="41">
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>rendement en char</t>
+          <t>rapport fibres/résine</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -1390,7 +1411,7 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>idem — mais il entre dans le CALCUL du gaz pour les routes C et D</t>
+          <t>fixe la QUANTITÉ de gaz (donc B'g), pas sa composition</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr"/>
@@ -1401,17 +1422,17 @@
     <row r="42">
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>cinétique de pyrolyse</t>
+          <t>rendement en char</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>non *</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>fixe B'g au cours du temps</t>
+          <t>idem — mais il entre dans le CALCUL du gaz pour les routes C et D</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr"/>
@@ -1420,81 +1441,102 @@
       <c r="H42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>cinétique de pyrolyse</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>fixe B'g au cours du temps</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr"/>
+      <c r="F43" s="15" t="inlineStr"/>
+      <c r="G43" s="15" t="inlineStr"/>
+      <c r="H43" s="15" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>* sauf si les constituants donnent des chars de compositions élémentaires DIFFÉRENTES (fibres de silice + résine phénolique), ou si le renfort pyrolyse (liège) : le rapport entre alors dans Y_c et/ou Y_g, et la table change. Le bilan de masse de surface est écrit sur des fractions massiques élémentaires, donc normalisées : les grandeurs VOLUMIQUES n'y ont structurellement aucune place.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>§6 — RECETTE POUR UN NOUVEAU MATÉRIAU</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Atmosphère → composition -bl (air, Mars, Titan…).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Résine → composition du gaz de pyrolyse par l'une des quatre routes du §4 → composition -py.</t>
+          <t>Atmosphère → composition -bl (air, Mars, Titan…).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Char → C:1.0 si tous les constituants carbonisent vers le carbone ; sinon pondérer par les masses de char de chaque constituant.</t>
+          <t>Résine → composition du gaz de pyrolyse par l'une des quatre routes du §4 → composition -py.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Espèces → tous les produits attendus des éléments présents, PLUS la ou les phases condensées.</t>
+          <t>Char → C:1.0 si tous les constituants carbonisent vers le carbone ; sinon pondérer par les masses de char de chaque constituant.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Vérifier : checkmix (noms, phases), puis un run court.</t>
+          <t>Espèces → tous les produits attendus des éléments présents, PLUS la ou les phases condensées.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Vérifier : checkmix (noms, phases), puis un run court.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Contrôler la physique : à 300 K et B'g = 0 dans l'air, un char carboné doit donner B'c ≈ 0.0874 (limite C + O2 → CO2, indépendante de la pression). Une valeur ≈ 200 signale l'absence de C(gr).</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="B53" s="5" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Documents de référence du dépôt : tacot_bprime/mise_en_donnees_xml.md (mécanique du fichier XML et règles du parseur) · resine_tacot.md · zuram_bprime/resine_zuram.md · sc1008_bprime/resine_sc1008.md · cork_bprime/mise_en_donnees_cork.md · tacot_bprime/cph70_vs_tacot.md · carbon_bprime/bprime_carbon_physique.md.</t>
         </is>
@@ -1503,27 +1545,694 @@
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="B7:I7"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A46:I46"/>
     <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B46:I46"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B52:I52"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A22:I22"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="B44:I44"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="B19:I19"/>
     <mergeCell ref="B49:I49"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B50:I50"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000070C0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4.5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="72" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Silice SiO2 — char MULTI-ÉLÉMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Le seul matériau du dépôt dont le char n'est pas du carbone : montre comment se remplit une composition à plusieurs éléments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Fichier(s) XML : data/mixtures/silica-air.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>§0 — FICHE D'IDENTITÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Matériau</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>silice pure SiO2</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>silice_bprime/silice_bprime.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Système chimique</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Si-N-O : 5 espèces d'air + 5 espèces gazeuses du silicium + 4 phases condensées de SiO2</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>SiO2(a-qz), SiO2(b-qz), SiO2(b-crt), SiO2(L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Binaire dédié</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>bprime_silica (et non bprime)</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>le bilan est résolu sur Si, pas sur C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Compositions du XML</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>air (-bl) · silice (char, -char-elem Si)</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>§1 — HYPOTHÈSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Le char est la silice elle-même, de stœchiométrie SiO2 exacte.</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>Matériau monolithique : pas de résine, donc pas de gaz de pyrolyse (B'g = 0) et pas de fermeture élémentaire à faire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>L'élément du bilan est le SILICIUM, pas le carbone.</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Règle générale : `-char-elem` doit désigner un élément PRÉSENT dans le char et ABSENT (ou minoritaire) au bord de couche limite. L'oxygène ne conviendrait pas — l'air en contient 21 % molaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Les quatre phases condensées de SiO2 doivent figurer dans &lt;species&gt;.</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>Même exigence que C(gr) pour les matériaux carbonés : sans phase condensée, le solveur ne peut pas faire précipiter la silice et B'c sature sur une valeur non physique. Ici il faut les quatre polymorphes (quartz α et β, cristobalite β, liquide) pour couvrir toute la plage de température.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Équilibre thermochimique à la paroi.</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>Identique aux autres matériaux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>§2 — DONNÉES D'ENTRÉE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>stœchiométrie — ν_Si</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>stœchiométrie — ν_O</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>masse volumique de la silice [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>silice vitreuse — n'entre que dans la récession</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>§3 — CALCUL PAS À PAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Étape 1 — masse molaire du motif</t>
+        </is>
+      </c>
+      <c r="I23" s="27" t="inlineStr">
+        <is>
+          <t>M = ν_Si·M_Si + ν_O·M_O</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>M(SiO2) [g/mol]</t>
+        </is>
+      </c>
+      <c r="C24" s="70">
+        <f>C18*Constantes!$C$11+C19*Constantes!$C$9</f>
+        <v>60.0835</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>attendu 60.08 g/mol</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Étape 2 — composition élémentaire, en molaire puis en massique</t>
+        </is>
+      </c>
+      <c r="I25" s="27" t="inlineStr">
+        <is>
+          <t>x_E = ν_E / Σ ν_j ;  y_E = ν_E·M_E / M</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Somme</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>ν_E (moles d'atomes par motif)</t>
+        </is>
+      </c>
+      <c r="C27" s="24">
+        <f>C18</f>
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="24">
+        <f>C19</f>
+        <v>2.0</v>
+      </c>
+      <c r="E27" s="24">
+        <f>SUM(C27:D27)</f>
+        <v>3.0</v>
+      </c>
+      <c r="F27" s="15" t="inlineStr"/>
+      <c r="G27" s="15" t="inlineStr"/>
+      <c r="H27" s="15" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>x_E (fraction molaire élémentaire, normalisée)</t>
+        </is>
+      </c>
+      <c r="C28" s="26">
+        <f>C27/$E$27</f>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D28" s="26">
+        <f>D27/$E$27</f>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E28" s="24">
+        <f>SUM(C28:D28)</f>
+        <v>1.0</v>
+      </c>
+      <c r="F28" s="15" t="inlineStr"/>
+      <c r="G28" s="15" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>y_E (fraction massique élémentaire)</t>
+        </is>
+      </c>
+      <c r="C29" s="26">
+        <f>C27*Constantes!$C$11/$C$24</f>
+        <v>0.4674411444073664</v>
+      </c>
+      <c r="D29" s="26">
+        <f>D27*Constantes!$C$9/$C$24</f>
+        <v>0.5325588555926336</v>
+      </c>
+      <c r="E29" s="24">
+        <f>SUM(C29:D29)</f>
+        <v>1.0</v>
+      </c>
+      <c r="F29" s="15" t="inlineStr"/>
+      <c r="G29" s="15" t="inlineStr"/>
+      <c r="H29" s="15" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Attendu : x_Si = 0.3333 / x_O = 0.6667 en molaire, y_Si = 0.4674 / y_O = 0.5326 en masse. Le piège classique est de confondre les deux — le parseur suppose du MOLAIRE par défaut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§4 — RÉSULTAT : CE QUI ENTRE DANS LE XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Composition élémentaire</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Somme</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>après normalisation par le parseur</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>valeur portée dans le XML (silice)</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="24">
+        <f>SUM(C34:D34)</f>
+        <v>3.0</v>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>x_Si = 1/3, x_O = 2/3</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>C'est l'illustration la plus nette de la règle de normalisation automatique (Composition::componentsFromList) : « Si:1.0, O:2.0 » somme à 3, et le parseur le ramène à 1. On peut donc saisir indifféremment des moles brutes, des pourcentages ou des fractions — c'est le RAPPORT qui compte, et écrire directement Si:0.3333, O:0.6667 donnerait exactement le même mélange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>§5 — CONTRÔLES ET VALIDATION CROISÉE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>x_Si + x_O après normalisation</t>
+        </is>
+      </c>
+      <c r="C38" s="60">
+        <f>C28+D28</f>
+        <v>1.0</v>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>doit valoir 1 exactement</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>rapport O/Si</t>
+        </is>
+      </c>
+      <c r="C39" s="70">
+        <f>D27/C27</f>
+        <v>2.0</v>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>doit valoir 2 — la stœchiométrie de la silice</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Le cas de la silice est aussi le CONTRE-EXEMPLE de référence pour les composites : dès que les constituants ne carbonisent pas vers le même produit (fibres de silice + résine phénolique, par exemple), le char devient multi-élément et il faut pondérer par les MASSES de char de chaque constituant : n_E(char) = Σ_i (m_char,i / M_i)·ν_E,i. Le ratio renfort/résine entre alors dans la table B' — cf. onglet CPh70 §6 pour le cas contraire, et l'onglet Liège-phénolique §5 pour un exemple chiffré de pondération.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>§6 — SENSIBILITÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Sans objet : la stœchiométrie SiO2 est exacte, il n'y a ni rendement en char, ni analyse élémentaire, ni motif de résine à choisir. C'est la mise en données la moins incertaine du classeur — l'incertitude est reportée sur la base thermodynamique des quatre phases condensées et sur l'hypothèse d'équilibre à la paroi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>§7 — RÉPONSE MATÉRIAU (n'entre PAS dans le XML)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="35" t="inlineStr">
+        <is>
+          <t>couplage k = B'g / B'c</t>
+        </is>
+      </c>
+      <c r="C46" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>pas de pyrolyse interne — comme le graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>ρ_char [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C47" s="73">
+        <f>C20</f>
+        <v>2200.0</v>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>la silice fondue est évacuée mécaniquement : la récession réelle dépasse celle donnée par B'c seul</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>§8 — BLOC XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>&lt;mixture thermo_db="NASA-9"&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;species&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        N O NO N2 O2 Si SiO SiO2 Si2 SiN SiO2(a-qz) SiO2(b-qz) SiO2(b-crt) SiO2(L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/species&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;element_compositions default="air"&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;composition name="air"&gt;N:0.79, O:0.21&lt;/composition&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;composition name="silice"&gt;Si:1.0, O:2.0&lt;/composition&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/element_compositions&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="29" t="inlineStr">
+        <is>
+          <t>&lt;/mixture&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>bprime_silica -T 300:25:5000 -P &lt;P&gt; -b 0.0 -m silica-air -bl air</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B55:I55"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A45:I45"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B50:I50"/>
-    <mergeCell ref="B26:I26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9583,6 +10292,1909 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I124"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4.5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="72" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MX-4926 — carbone/phénolique chargé noir de carbone</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Matrice SC-1008 : le gaz est HÉRITÉ · démontre que le taux de charge n'entre pas dans le XML, et que la fermeture Σw = 1 tronque une des plages annoncées</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Fichier(s) XML : data/mixtures/mx4926-air.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>§0 — FICHE D'IDENTITÉ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Matériau</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>MX-4926 — carbone/phénolique chargé</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>matériau de tuyère de moteur à propergol solide</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Renfort</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>fibres de carbone ex-rayon (ex-cellulose), tissu satin de 5 ou de 8</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>le satin accommode les formes complexes et tient la stabilité dimensionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Matrice</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>résol phénol-formaldéhyde SC-1008 — IDENTIQUE au PICA</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>cf. onglet SC-1008 §0 ; liant à haut rendement en char</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>noir de carbone</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>optimise l'isolation thermique et la formation du char</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Source du gaz</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>route C, HÉRITÉE du SC-1008 (résine inchangée)</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>mx4926_bprime/composition_mx4926.md §2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Compositions du XML</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>air (-bl) · mx4926_pyro (-py) · mx4926_char (-char, -char-elem C)</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>mx4926_bprime/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>§1 — HYPOTHÈSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>La matrice est RIGOUREUSEMENT le SC-1008 de l'onglet précédent : même motif C7.5H6O, même rendement en char.</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>C'est la seule chose dont dépend la composition du gaz. Tout le §3 de l'onglet SC-1008 s'applique tel quel et n'est PAS refait ici.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Le renfort ex-rayon ne dégaze pas : une fibre de carbone est déjà le produit d'une pyrolyse.</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>Perte de masse nulle jusqu'au domaine de sublimation. Contre-exemple : le liège, qui pyrolyse — son onglet doit alors fermer sur DEUX constituants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Le noir de carbone est inerte et ne dégaze pas non plus.</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Carbone quasi pur (97-99 % C). Du point de vue du bilan de surface il se comporte exactement comme des fibres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Les trois constituants carbonisent vers le carbone pur ⇒ char C:1.0 quelles que soient les proportions.</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>La pondération n_E(char) = Σ_i (m_char,i/M_i)·ν_E,i se réduit à C:1.0 dès que tous les constituants donnent le même élément.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Aucune grandeur volumique n'entre dans le bilan de surface.</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Le bilan est écrit sur des fractions massiques élémentaires, donc normalisées : ni ρ, ni porosité (Constantes §4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>H6</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Les trois plages de composition annoncées doivent se refermer à 100 %.</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>Elles sont données indépendamment les unes des autres, mais ne peuvent pas l'être : c'est l'objet de l'étape 1 du §3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>§2 — DONNÉES D'ENTRÉE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Fractions MASSIQUES annoncées</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>borne basse</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>borne haute</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>renfort — fibres de carbone ex-rayon</t>
+        </is>
+      </c>
+      <c r="C23" s="51" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="D23" s="51" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr"/>
+      <c r="F23" s="15" t="inlineStr"/>
+      <c r="G23" s="15" t="inlineStr"/>
+      <c r="H23" s="15" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>matrice — résol SC-1008</t>
+        </is>
+      </c>
+      <c r="C24" s="51" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D24" s="51" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="inlineStr"/>
+      <c r="G24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>charge — noir de carbone</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D25" s="51" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr"/>
+      <c r="F25" s="15" t="inlineStr"/>
+      <c r="G25" s="15" t="inlineStr"/>
+      <c r="H25" s="15" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>SOMME</t>
+        </is>
+      </c>
+      <c r="C26" s="23">
+        <f>SUM(C23:C25)</f>
+        <v>0.83</v>
+      </c>
+      <c r="D26" s="23">
+        <f>SUM(D23:D25)</f>
+        <v>1.09</v>
+      </c>
+      <c r="E26" s="15" t="inlineStr"/>
+      <c r="F26" s="15" t="inlineStr"/>
+      <c r="G26" s="15" t="inlineStr"/>
+      <c r="H26" s="15" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Ces deux sommes sont le point de départ de tout l'onglet : 0.830 et 1.090. Elles encadrent 1 sans le valoir — les trois plages ne sont donc pas indépendantes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>rendement en char de la RÉSINE, Y</t>
+        </is>
+      </c>
+      <c r="C28" s="62">
+        <f>'SC-1008'!C23</f>
+        <v>0.55</v>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>lien vers l'onglet SC-1008 §2 : 0.55, recoupement [TS] et ATG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>ρ intrinsèque fibres [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>fibres ex-cellulose — Description!A11 du classeur TACOT 3.0 ; le rayon EST une cellulose régénérée</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>ρ intrinsèque résol cuit [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>valeur usuelle d'un phénolique cuit (1200-1300)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>ρ intrinsèque noir de carbone [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>valeur usuelle (1800-2100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>densité publiée du MX-4926 [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="n">
+        <v>1450</v>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>≈ 1.45 g/cm³ — sert au contrôle C du §5, pas au calcul</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>§3 — CALCUL PAS À PAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Étape 1 — FERMETURE : les plages effectives ne sont pas les plages annoncées</t>
+        </is>
+      </c>
+      <c r="I35" s="27" t="inlineStr">
+        <is>
+          <t>w_i,min_eff = MAX(w_i,min ; 1 − Σ_{j≠i} w_j,max)   et symétriquement</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Plages EFFECTIVES après fermeture</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>annoncé min</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>annoncé max</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>largeur perdue</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>renfort</t>
+        </is>
+      </c>
+      <c r="C37" s="24">
+        <f>MAX(C23,1-D24-D25)</f>
+        <v>0.47</v>
+      </c>
+      <c r="D37" s="24">
+        <f>MIN(D23,1-C24-C25)</f>
+        <v>0.56</v>
+      </c>
+      <c r="E37" s="25">
+        <f>C23</f>
+        <v>0.41</v>
+      </c>
+      <c r="F37" s="25">
+        <f>D23</f>
+        <v>0.56</v>
+      </c>
+      <c r="G37" s="23">
+        <f>(D23-C23)-(D37-C37)</f>
+        <v>0.06</v>
+      </c>
+      <c r="H37" s="15" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>matrice</t>
+        </is>
+      </c>
+      <c r="C38" s="24">
+        <f>MAX(C24,1-D23-D25)</f>
+        <v>0.31</v>
+      </c>
+      <c r="D38" s="24">
+        <f>MIN(D24,1-C23-C25)</f>
+        <v>0.37</v>
+      </c>
+      <c r="E38" s="25">
+        <f>C24</f>
+        <v>0.31</v>
+      </c>
+      <c r="F38" s="25">
+        <f>D24</f>
+        <v>0.37</v>
+      </c>
+      <c r="G38" s="23">
+        <f>(D24-C24)-(D38-C38)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H38" s="15" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="C39" s="24">
+        <f>MAX(C25,1-D23-D24)</f>
+        <v>0.11</v>
+      </c>
+      <c r="D39" s="24">
+        <f>MIN(D25,1-C23-C24)</f>
+        <v>0.16</v>
+      </c>
+      <c r="E39" s="25">
+        <f>C25</f>
+        <v>0.11</v>
+      </c>
+      <c r="F39" s="25">
+        <f>D25</f>
+        <v>0.16</v>
+      </c>
+      <c r="G39" s="23">
+        <f>(D25-C25)-(D39-C39)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H39" s="15" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Une seule ligne a une largeur perdue non nulle : le RENFORT, dont la borne basse passe de 41 % à 47 %. Pour descendre à 41 % de fibres il faudrait 59 % de résine + charge, alors que le maximum admissible est 37 + 16 = 53 %. Les 41 % annoncés ne sont atteignables avec AUCUN couple (résine, charge) admissible. Les plages de la matrice et de la charge survivent intactes — et c'est la matrice qui pilote toute la suite (étape 4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Étape 2 — composition retenue : le centroïde du domaine admissible</t>
+        </is>
+      </c>
+      <c r="I41" s="27" t="inlineStr">
+        <is>
+          <t>centroïde d'AIRE du polygone (5 sommets), pas une moyenne de grille</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Composition retenue (fractions massiques)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>renfort</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>matrice</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Somme</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>centroïde exact du polygone admissible</t>
+        </is>
+      </c>
+      <c r="C43" s="63" t="n">
+        <v>0.52202381</v>
+      </c>
+      <c r="D43" s="63" t="n">
+        <v>0.34166667</v>
+      </c>
+      <c r="E43" s="64">
+        <f>1-C43-D43</f>
+        <v>0.13630952000000002</v>
+      </c>
+      <c r="F43" s="64">
+        <f>SUM(C43:E43)</f>
+        <v>1.0</v>
+      </c>
+      <c r="G43" s="15" t="inlineStr"/>
+      <c r="H43" s="15" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Les deux valeurs bleues sont produites par mx4926_bprime/composition_mx4926_verification.py §2 (clipping de Sutherland-Hodgman, puis formule du centroïde d'aire) : un polygone à 5 sommets ne se moyenne pas à la main. La CHARGE n'est pas saisie : elle est fermée par différence, de sorte que Σw = 1 exactement quel que soit l'arrondi des deux autres — saisir les trois arrondies à 1e-6 briserait la fermeture de 1e-6. Le contrôle D du §5 vérifie que le point tombe bien dans les plages effectives ci-dessus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Étape 3 — gaz de pyrolyse : HÉRITÉ, pas recalculé</t>
+        </is>
+      </c>
+      <c r="I45" s="27" t="inlineStr">
+        <is>
+          <t>Y_g(MX-4926) = Y_g(SC-1008), par H1 + H2 + H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Gaz de pyrolyse</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Somme</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>H/O</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>reprise de l'onglet SC-1008 (fermeture élémentaire, route C)</t>
+        </is>
+      </c>
+      <c r="C47" s="8">
+        <f>'SC-1008'!C48</f>
+        <v>0.2525709901765317</v>
+      </c>
+      <c r="D47" s="8">
+        <f>'SC-1008'!D48</f>
+        <v>0.6406534369915442</v>
+      </c>
+      <c r="E47" s="8">
+        <f>'SC-1008'!E48</f>
+        <v>0.10677557283192403</v>
+      </c>
+      <c r="F47" s="24">
+        <f>SUM(C47:E47)</f>
+        <v>0.9999999999999999</v>
+      </c>
+      <c r="G47" s="9">
+        <f>D47/E47</f>
+        <v>6.0</v>
+      </c>
+      <c r="H47" s="15" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Le gaz est produit par la RÉSINE SEULE. Le renfort ex-rayon est déjà carbonisé (H2) et le noir de carbone est inerte (H3) : aucun des deux ne dégaze. La matrice étant le SC-1008, la composition élémentaire du gaz est celle du SC-1008 — toute sa traçabilité (motif C7.5H6O, fermeture à Y = 0.55, confrontation à [TS]) est celle de l'onglet précédent. Le taux de charge et le rapport fibres/résine changent la QUANTITÉ de gaz produite, donc B'g, qui est un paramètre d'ENTRÉE de la table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Étape 4 — char : pondération générale des TROIS constituants</t>
+        </is>
+      </c>
+      <c r="I49" s="27" t="inlineStr">
+        <is>
+          <t>n_E(char) = Σ_i (m_char,i / M_i) · ν_E,i</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Fibres ex-rayon : carbone pur. Noir de carbone : carbone pur. Résol carbonisé : carbone pur. La somme pondérée de trois compositions identiques est cette composition, quelles que soient les masses : le char vaut C:1.0 pour TOUT jeu de proportions. C'est ce qui rendrait le calcul faux avec des fibres de silice, un char retenant H/O, ou une charge non carbonée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Étape 5 — rendement en char du COMPOSITE : la fermeture le simplifie</t>
+        </is>
+      </c>
+      <c r="I51" s="27" t="inlineStr">
+        <is>
+          <t>Y_comp = w_f + w_c + Y·w_r = 1 − (1 − Y)·w_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Rendement en char du composite</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>forme longue</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>forme courte</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>écart</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Y_comp</t>
+        </is>
+      </c>
+      <c r="C53" s="56">
+        <f>C43+E43+$C$28*D43</f>
+        <v>0.8462499985</v>
+      </c>
+      <c r="D53" s="56">
+        <f>1-(1-$C$28)*D43</f>
+        <v>0.8462499985</v>
+      </c>
+      <c r="E53" s="59">
+        <f>C53-D53</f>
+        <v>0.0</v>
+      </c>
+      <c r="F53" s="15" t="inlineStr"/>
+      <c r="G53" s="15" t="inlineStr"/>
+      <c r="H53" s="15" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>LE POINT DE CET ONGLET. Le renfort et la charge ne perdent pas de masse (H2, H3) ; en utilisant w_f + w_c = 1 − w_r, les deux disparaissent de l'expression. Y_comp — donc k, donc le point de fonctionnement — ne dépend QUE de la fraction de RÉSINE. Le partage fibres/charge n'a aucun effet, et l'incertitude sur le renfort mise en évidence à l'étape 1 est sans conséquence sur la réponse matériau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>Étape 6 — couplage et densités</t>
+        </is>
+      </c>
+      <c r="I55" s="27" t="inlineStr">
+        <is>
+          <t>k = (ρ_v − ρ_c)/ρ_c = (1 − Y_comp)/Y_comp ;  ρ_v = (1 − φ)/Σ_i (w_i/ρ_i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="35" t="inlineStr">
+        <is>
+          <t>couplage k = B'g / B'c</t>
+        </is>
+      </c>
+      <c r="C56" s="46">
+        <f>(1-C53)/C53</f>
+        <v>0.18168390165143375</v>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>attendu 0.1817 — la SEULE grandeur qui distingue le MX-4926 du SC-1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="35" t="inlineStr">
+        <is>
+          <t>porosité φ</t>
+        </is>
+      </c>
+      <c r="C57" s="37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I57" s="12" t="inlineStr">
+        <is>
+          <t>contrôlée au §5 : c'est celle qui restitue la densité publiée</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="35" t="inlineStr">
+        <is>
+          <t>volume de solide par kg [m³/kg]</t>
+        </is>
+      </c>
+      <c r="C58" s="65">
+        <f>C43/$C$29+D43/$C$30+E43/$C$31</f>
+        <v>0.0006753257283611112</v>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>Σ w_i/ρ_i</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="35" t="inlineStr">
+        <is>
+          <t>ρ vierge [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C59" s="45">
+        <f>(1-C57)/C58</f>
+        <v>1451.1515833674457</v>
+      </c>
+      <c r="I59" s="12" t="inlineStr">
+        <is>
+          <t>attendu 1451 (PICA : 274 · TACOT : 280 · CPh70 : 1465)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="35" t="inlineStr">
+        <is>
+          <t>ρ char [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C60" s="45">
+        <f>C59*C53</f>
+        <v>1228.0370252479736</v>
+      </c>
+      <c r="I60" s="12" t="inlineStr">
+        <is>
+          <t>attendu 1228</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="35" t="inlineStr">
+        <is>
+          <t>gaz de pyrolyse libéré [kg/m³]</t>
+        </is>
+      </c>
+      <c r="C61" s="45">
+        <f>C59-C60</f>
+        <v>223.11455811947212</v>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>attendu 223.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="35" t="inlineStr">
+        <is>
+          <t>… soit en % de la masse vierge</t>
+        </is>
+      </c>
+      <c r="C62" s="47">
+        <f>(1-C53)*100</f>
+        <v>15.375000149999995</v>
+      </c>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>15.4 % — contre 21.4 % pour le TACOT et 12.2 % pour le CPh70</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>k est un rapport de MASSES : ni les densités ni la porosité n'y entrent — elles ne servent qu'à la récession ṡ = B'c·ṁe/ρ_c. C'est pourquoi l'incertitude sur ρ des constituants, réelle, ne se propage pas au point de fonctionnement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>§4 — RÉSULTAT : CE QUI ENTRE DANS LE XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Composition élémentaire (fractions molaires)</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Somme</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>calcul — chaîne complète ci-dessus</t>
+        </is>
+      </c>
+      <c r="C67" s="26">
+        <f>C47</f>
+        <v>0.2525709901765317</v>
+      </c>
+      <c r="D67" s="26">
+        <f>D47</f>
+        <v>0.6406534369915442</v>
+      </c>
+      <c r="E67" s="26">
+        <f>E47</f>
+        <v>0.10677557283192403</v>
+      </c>
+      <c r="F67" s="24">
+        <f>SUM(C67:E67)</f>
+        <v>0.9999999999999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>valeur portée dans le XML (mx4926_pyro)</t>
+        </is>
+      </c>
+      <c r="C68" s="42" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="D68" s="42" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="E68" s="42" t="n">
+        <v>0.1068</v>
+      </c>
+      <c r="F68" s="24">
+        <f>SUM(C68:E68)</f>
+        <v>1.0001</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>écart relatif |calcul − XML| / XML</t>
+        </is>
+      </c>
+      <c r="C69" s="43">
+        <f>ABS(C67-C68)/C68</f>
+        <v>0.0001148449068421133</v>
+      </c>
+      <c r="D69" s="43">
+        <f>ABS(D67-D68)/D68</f>
+        <v>7.267521219891774e-05</v>
+      </c>
+      <c r="E69" s="43">
+        <f>ABS(E67-E68)/E68</f>
+        <v>0.00022871880220952454</v>
+      </c>
+      <c r="F69" s="15" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Char (mx4926_char)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>composition du XML</t>
+        </is>
+      </c>
+      <c r="C71" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr"/>
+      <c r="G71" s="15" t="inlineStr"/>
+      <c r="H71" s="15" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Le fichier mx4926-air.xml est donc STRICTEMENT identique à sc1008-air.xml — même liste d'espèces, mêmes trois compositions. Il n'est justifié que par la traçabilité : nommer le matériau. Pour les propriétés du gaz de pyrolyse seul (h_g, Cp, M, γ), il n'y a pas non plus de fichier propre : sc1008-pyrogas.xml est valable tel quel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>§5 — CONTRÔLES ET VALIDATION CROISÉE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>Contrôle A — identité BIT À BIT de la table B' avec celle du SC-1008</t>
+        </is>
+      </c>
+      <c r="I75" s="27" t="inlineStr">
+        <is>
+          <t>diff caractère pour caractère de la sortie de `bprime`</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>B'g testé</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>lignes comparées</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>lignes différentes</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="6" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="40" t="n">
+        <v>149</v>
+      </c>
+      <c r="D77" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="15" t="inlineStr"/>
+      <c r="F77" s="15" t="inlineStr"/>
+      <c r="G77" s="15" t="inlineStr"/>
+      <c r="H77" s="15" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C78" s="40" t="n">
+        <v>149</v>
+      </c>
+      <c r="D78" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr"/>
+      <c r="G78" s="15" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C79" s="40" t="n">
+        <v>149</v>
+      </c>
+      <c r="D79" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="15" t="inlineStr"/>
+      <c r="F79" s="15" t="inlineStr"/>
+      <c r="G79" s="15" t="inlineStr"/>
+      <c r="H79" s="15" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="40" t="n">
+        <v>149</v>
+      </c>
+      <c r="D80" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="15" t="inlineStr"/>
+      <c r="F80" s="15" t="inlineStr"/>
+      <c r="G80" s="15" t="inlineStr"/>
+      <c r="H80" s="15" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Produit par `python mx4926_bprime/composition_mx4926_verification.py` §5. Pas « proche » : identique caractère pour caractère, comme cph70-air_25 face à tacot-air_25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>Contrôle B — limite d'oxydation à 300 K</t>
+        </is>
+      </c>
+      <c r="I82" s="27" t="inlineStr">
+        <is>
+          <t>C + O2 → CO2, indépendante de la pression</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="35" t="inlineStr">
+        <is>
+          <t>B'c(300 K, B'g = 0, 1 atm)</t>
+        </is>
+      </c>
+      <c r="C83" s="60" t="n">
+        <v>0.087427</v>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>attendu 0.0874 — une valeur ≈ 200 signalerait l'absence de C(gr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>Contrôle C — la porosité retenue restitue-t-elle la densité publiée ?</t>
+        </is>
+      </c>
+      <c r="I84" s="27" t="inlineStr">
+        <is>
+          <t>φ = 1 − ρ_publié · Σ_i (w_i/ρ_i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="35" t="inlineStr">
+        <is>
+          <t>porosité déduite de la densité publiée</t>
+        </is>
+      </c>
+      <c r="C85" s="46">
+        <f>1-C32*C58</f>
+        <v>0.020777693876388836</v>
+      </c>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>0.0208 — à comparer au 0.02 retenu à l'étape 6 ; faible et positive, cohérent avec un composite dense pressé</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="35" t="inlineStr">
+        <is>
+          <t>écart sur ρ_v</t>
+        </is>
+      </c>
+      <c r="C86" s="67">
+        <f>ABS(C59-C32)/C32</f>
+        <v>0.0007941954258246275</v>
+      </c>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>la porosité n'est donc pas un paramètre libre : elle est fixée par la densité mesurée</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>Contrôle D — le centroïde referme-t-il, et tombe-t-il dans les plages effectives ?</t>
+        </is>
+      </c>
+      <c r="I87" s="27" t="inlineStr">
+        <is>
+          <t>marge = distance à la borne la plus proche ; elle doit être &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="35" t="inlineStr">
+        <is>
+          <t>défaut de fermeture |Σw − 1|</t>
+        </is>
+      </c>
+      <c r="C88" s="41">
+        <f>ABS(F43-1)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>nul par construction : la charge est fermée par différence (étape 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="35" t="inlineStr">
+        <is>
+          <t>marge du renfort dans [min_eff ; max_eff]</t>
+        </is>
+      </c>
+      <c r="C89" s="46">
+        <f>MIN(C43-C37,D37-C43)</f>
+        <v>0.037976190000000076</v>
+      </c>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>0.0380 — le centroïde est loin des deux bornes</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="35" t="inlineStr">
+        <is>
+          <t>marge de la matrice dans [min_eff ; max_eff]</t>
+        </is>
+      </c>
+      <c r="C90" s="46">
+        <f>MIN(D43-C38,D38-D43)</f>
+        <v>0.02833332999999999</v>
+      </c>
+      <c r="I90" s="12" t="inlineStr">
+        <is>
+          <t>0.0283 — idem</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>§6 — SENSIBILITÉ : SEULE LA FRACTION DE RÉSINE COMPTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>w_résine testé</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Y_comp</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>k = B'g/B'c</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>B'c stationnaire 1 atm 3000 K</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>gaz — C</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>gaz — H</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>gaz — O</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C94" s="26">
+        <f>1-(1-$C$28)*B94</f>
+        <v>0.8605</v>
+      </c>
+      <c r="D94" s="26">
+        <f>(1-C94)/C94</f>
+        <v>0.16211504938988955</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>0.18171</v>
+      </c>
+      <c r="F94" s="8">
+        <f>$C$47</f>
+        <v>0.2525709901765317</v>
+      </c>
+      <c r="G94" s="8">
+        <f>$D$47</f>
+        <v>0.6406534369915442</v>
+      </c>
+      <c r="H94" s="8">
+        <f>$E$47</f>
+        <v>0.10677557283192403</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="21" t="n">
+        <v>0.341667</v>
+      </c>
+      <c r="C95" s="26">
+        <f>1-(1-$C$28)*B95</f>
+        <v>0.84624985</v>
+      </c>
+      <c r="D95" s="26">
+        <f>(1-C95)/C95</f>
+        <v>0.1816841090134315</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>0.18187</v>
+      </c>
+      <c r="F95" s="8">
+        <f>$C$47</f>
+        <v>0.2525709901765317</v>
+      </c>
+      <c r="G95" s="8">
+        <f>$D$47</f>
+        <v>0.6406534369915442</v>
+      </c>
+      <c r="H95" s="8">
+        <f>$E$47</f>
+        <v>0.10677557283192403</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="21" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="C96" s="26">
+        <f>1-(1-$C$28)*B96</f>
+        <v>0.8335</v>
+      </c>
+      <c r="D96" s="26">
+        <f>(1-C96)/C96</f>
+        <v>0.1997600479904019</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>0.18203</v>
+      </c>
+      <c r="F96" s="8">
+        <f>$C$47</f>
+        <v>0.2525709901765317</v>
+      </c>
+      <c r="G96" s="8">
+        <f>$D$47</f>
+        <v>0.6406534369915442</v>
+      </c>
+      <c r="H96" s="8">
+        <f>$E$47</f>
+        <v>0.10677557283192403</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Les trois dernières colonnes sont CONSTANTES : c'est la démonstration de cet onglet, comme pour le CPh70. Toute la plage de composition annoncée (31-37 % de résine) déplace k de 0.162 à 0.200 et ne touche pas d'un iota la composition portée dans le XML — ni, en pratique, le B'c stationnaire : 0.18 % d'étendue à 3000 K, 1.07 % à 2000 K, 4.6 % seulement au genou de sublimation à 3700 K. Ce n'est pas le paramètre à resserrer en priorité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Sensibilité au partage fibres/charge</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>renfort</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Y_comp</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>w_résine gelé au centroïde</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D99" s="21" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="E99" s="26">
+        <f>1-(1-$C$28)*$D$43</f>
+        <v>0.8462499985</v>
+      </c>
+      <c r="F99" s="26">
+        <f>(1-E99)/E99</f>
+        <v>0.18168390165143375</v>
+      </c>
+      <c r="G99" s="15" t="inlineStr"/>
+      <c r="H99" s="15" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>w_résine gelé au centroïde</t>
+        </is>
+      </c>
+      <c r="C100" s="21" t="n">
+        <v>0.522024</v>
+      </c>
+      <c r="D100" s="21" t="n">
+        <v>0.13631</v>
+      </c>
+      <c r="E100" s="26">
+        <f>1-(1-$C$28)*$D$43</f>
+        <v>0.8462499985</v>
+      </c>
+      <c r="F100" s="26">
+        <f>(1-E100)/E100</f>
+        <v>0.18168390165143375</v>
+      </c>
+      <c r="G100" s="15" t="inlineStr"/>
+      <c r="H100" s="15" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>w_résine gelé au centroïde</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D101" s="21" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E101" s="26">
+        <f>1-(1-$C$28)*$D$43</f>
+        <v>0.8462499985</v>
+      </c>
+      <c r="F101" s="26">
+        <f>(1-E101)/E101</f>
+        <v>0.18168390165143375</v>
+      </c>
+      <c r="G101" s="15" t="inlineStr"/>
+      <c r="H101" s="15" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>Colonnes Y_comp et k STRICTEMENT constantes : déplacer 9 points de masse du renfort vers la charge ne change rien. Les deux sont du carbone à perte de masse nulle — seule leur SOMME compte, et la fermeture la fixe à 1 − w_résine. (Les couples ci-dessus ne referment volontairement pas à 1 avec w_résine : ils n'illustrent que le partage.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>§7 — RÉPONSE MATÉRIAU (n'entre PAS dans le XML)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Matériau</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>k = B'g/B'c</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="6" t="inlineStr"/>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>TACOT (10/10/80 vol.)</t>
+        </is>
+      </c>
+      <c r="C106" s="8">
+        <f>'TACOT'!C103</f>
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>poreux — beaucoup de résine par unité de masse</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr"/>
+      <c r="F106" s="15" t="inlineStr"/>
+      <c r="G106" s="15" t="inlineStr"/>
+      <c r="H106" s="15" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>PICA / SC-1008</t>
+        </is>
+      </c>
+      <c r="C107" s="8">
+        <f>'SC-1008'!C126</f>
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>même résine, sans charge, taux de résine plus élevé</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr"/>
+      <c r="F107" s="15" t="inlineStr"/>
+      <c r="G107" s="15" t="inlineStr"/>
+      <c r="H107" s="15" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>MX-4926</t>
+        </is>
+      </c>
+      <c r="C108" s="68">
+        <f>C56</f>
+        <v>0.18168390165143375</v>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>dense et chargé</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr"/>
+      <c r="F108" s="15" t="inlineStr"/>
+      <c r="G108" s="15" t="inlineStr"/>
+      <c r="H108" s="15" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>CPh70 (69/30/1 vol.)</t>
+        </is>
+      </c>
+      <c r="C109" s="8">
+        <f>'CPh70'!C43</f>
+        <v>0.13846153846153833</v>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>dense et très riche en fibres</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr"/>
+      <c r="F109" s="15" t="inlineStr"/>
+      <c r="G109" s="15" t="inlineStr"/>
+      <c r="H109" s="15" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>Le noir de carbone agit exactement comme des fibres du point de vue du bilan : il ajoute de la masse qui ne dégaze pas, donc il ABAISSE k. Le MX-4926 se place entre le PICA — même résine, mais sans charge — et le CPh70.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="35" t="inlineStr">
+        <is>
+          <t>rapport ρ_char MX-4926 / ρ_char TACOT</t>
+        </is>
+      </c>
+      <c r="C111" s="47">
+        <f>C60/'TACOT'!C101</f>
+        <v>5.58198647839988</v>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>à B'c égal, la récession ṡ = B'c·ṁe/ρ_c du MX-4926 est ~5.6 fois plus lente</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>§8 — BLOC XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="29" t="inlineStr">
+        <is>
+          <t>&lt;mixture thermo_db="NASA-9"&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;species&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       C H O N CH4 CN CO CO2 C2 C2H C2H2,acetylene C3 C4 C4H2,butadiyne C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       HCN H2 H2O N2 CH2OH CNN CNC CNCOCN C6H6 C6H5OH,phenol HNC C(gr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/species&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;element_compositions default="air"&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;composition name="air"&gt;N:0.79, O:0.21&lt;/composition&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;composition name="mx4926_pyro"&gt;C:0.2526, H:0.6407, O:0.1068&lt;/composition&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        &lt;composition name="mx4926_char"&gt;C:1.0&lt;/composition&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    &lt;/element_compositions&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="29" t="inlineStr">
+        <is>
+          <t>&lt;/mixture&gt;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="51">
+    <mergeCell ref="B97:I97"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B121:I121"/>
+    <mergeCell ref="B115:I115"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="B122:I122"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B102:I102"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A113:I113"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B120:I120"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B119:I119"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B116:I116"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="B118:I118"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B124:I124"/>
+    <mergeCell ref="B82:H82"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="B123:I123"/>
+    <mergeCell ref="B114:I114"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B110:I110"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B50:I50"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -9887,13 +12499,13 @@
           <t>liège [% masse]</t>
         </is>
       </c>
-      <c r="C24" s="62" t="n">
+      <c r="C24" s="69" t="n">
         <v>62.4</v>
       </c>
-      <c r="D24" s="62" t="n">
+      <c r="D24" s="69" t="n">
         <v>8.5</v>
       </c>
-      <c r="E24" s="62" t="n">
+      <c r="E24" s="69" t="n">
         <v>28.4</v>
       </c>
       <c r="F24" s="9">
@@ -10138,7 +12750,7 @@
           <t>fraction massique de résine dans le solide</t>
         </is>
       </c>
-      <c r="C38" s="63">
+      <c r="C38" s="70">
         <f>1-C37</f>
         <v>0.19999999999999996</v>
       </c>
@@ -10334,7 +12946,7 @@
           <t>y_liège = (y_comp − w_rés·y_rés) / w_liège</t>
         </is>
       </c>
-      <c r="C52" s="63">
+      <c r="C52" s="70">
         <f>($C$39-$C$38*$C$40)/$C$37</f>
         <v>0.12500000000000003</v>
       </c>
@@ -10622,7 +13234,7 @@
           <t>M du motif de résine [g/mol]</t>
         </is>
       </c>
-      <c r="C65" s="63">
+      <c r="C65" s="70">
         <f>C41*Constantes!$C$7+C42*Constantes!$C$8+C43*Constantes!$C$9</f>
         <v>106.124</v>
       </c>
@@ -11136,7 +13748,7 @@
           <t>y_liège par additivité</t>
         </is>
       </c>
-      <c r="C91" s="63">
+      <c r="C91" s="70">
         <f>SUMPRODUCT($C$29:$C$33,$H$29:$H$33)/$C$34</f>
         <v>0.24187500000000003</v>
       </c>
@@ -11152,7 +13764,7 @@
           <t>⇒ rendement du composite impliqué</t>
         </is>
       </c>
-      <c r="C92" s="63">
+      <c r="C92" s="70">
         <f>$C$37*C91+$C$38*$C$40</f>
         <v>0.2935</v>
       </c>
@@ -11710,7 +14322,7 @@
           <t>V_char / V_vierge impliqué</t>
         </is>
       </c>
-      <c r="C122" s="63">
+      <c r="C122" s="70">
         <f>$C$39*C44/C45</f>
         <v>0.3221030785195434</v>
       </c>
@@ -11870,7 +14482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00404040"/>
@@ -12366,7 +14978,7 @@
           <t>B'c attendu à 300 K, 1 atm</t>
         </is>
       </c>
-      <c r="C41" s="64">
+      <c r="C41" s="71">
         <f>C19*Constantes!$C$7/(2*Constantes!$C$9)</f>
         <v>0.08742648343329643</v>
       </c>
@@ -12435,17 +15047,17 @@
           <t>faible ablation</t>
         </is>
       </c>
-      <c r="C46" s="65" t="inlineStr">
+      <c r="C46" s="72" t="inlineStr">
         <is>
           <t>300 – 700</t>
         </is>
       </c>
-      <c r="D46" s="65" t="inlineStr">
+      <c r="D46" s="72" t="inlineStr">
         <is>
           <t>C(gr)</t>
         </is>
       </c>
-      <c r="E46" s="65" t="inlineStr">
+      <c r="E46" s="72" t="inlineStr">
         <is>
           <t>CO2, O2, N2</t>
         </is>
@@ -12464,17 +15076,17 @@
           <t>oxydation active</t>
         </is>
       </c>
-      <c r="C47" s="65" t="inlineStr">
+      <c r="C47" s="72" t="inlineStr">
         <is>
           <t>700 – 3500</t>
         </is>
       </c>
-      <c r="D47" s="65" t="inlineStr">
+      <c r="D47" s="72" t="inlineStr">
         <is>
           <t>C(gr)</t>
         </is>
       </c>
-      <c r="E47" s="65" t="inlineStr">
+      <c r="E47" s="72" t="inlineStr">
         <is>
           <t>CO, N2, CN</t>
         </is>
@@ -12493,17 +15105,17 @@
           <t>sublimation</t>
         </is>
       </c>
-      <c r="C48" s="65" t="inlineStr">
+      <c r="C48" s="72" t="inlineStr">
         <is>
           <t>3500 – 4000</t>
         </is>
       </c>
-      <c r="D48" s="65" t="inlineStr">
+      <c r="D48" s="72" t="inlineStr">
         <is>
           <t>C(gr) + gaz</t>
         </is>
       </c>
-      <c r="E48" s="65" t="inlineStr">
+      <c r="E48" s="72" t="inlineStr">
         <is>
           <t>CO, CN, C3</t>
         </is>
@@ -12522,17 +15134,17 @@
           <t>sublimation totale</t>
         </is>
       </c>
-      <c r="C49" s="65" t="inlineStr">
+      <c r="C49" s="72" t="inlineStr">
         <is>
           <t>&gt; 4000</t>
         </is>
       </c>
-      <c r="D49" s="65" t="inlineStr">
+      <c r="D49" s="72" t="inlineStr">
         <is>
           <t>gaz seul</t>
         </is>
       </c>
-      <c r="E49" s="65" t="inlineStr">
+      <c r="E49" s="72" t="inlineStr">
         <is>
           <t>C, C2, C3</t>
         </is>
@@ -12565,7 +15177,7 @@
           <t>couplage k = B'g / B'c</t>
         </is>
       </c>
-      <c r="C53" s="63" t="n">
+      <c r="C53" s="70" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="inlineStr">
@@ -12708,671 +15320,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000070C0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4.5" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="72" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Silice SiO2 — char MULTI-ÉLÉMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Le seul matériau du dépôt dont le char n'est pas du carbone : montre comment se remplit une composition à plusieurs éléments</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Fichier(s) XML : data/mixtures/silica-air.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>§0 — FICHE D'IDENTITÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>Matériau</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>silice pure SiO2</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>silice_bprime/silice_bprime.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>Système chimique</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>Si-N-O : 5 espèces d'air + 5 espèces gazeuses du silicium + 4 phases condensées de SiO2</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>SiO2(a-qz), SiO2(b-qz), SiO2(b-crt), SiO2(L)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>Binaire dédié</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>bprime_silica (et non bprime)</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>le bilan est résolu sur Si, pas sur C</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>Compositions du XML</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>air (-bl) · silice (char, -char-elem Si)</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>§1 — HYPOTHÈSES</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Le char est la silice elle-même, de stœchiométrie SiO2 exacte.</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>Matériau monolithique : pas de résine, donc pas de gaz de pyrolyse (B'g = 0) et pas de fermeture élémentaire à faire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>L'élément du bilan est le SILICIUM, pas le carbone.</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Règle générale : `-char-elem` doit désigner un élément PRÉSENT dans le char et ABSENT (ou minoritaire) au bord de couche limite. L'oxygène ne conviendrait pas — l'air en contient 21 % molaire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Les quatre phases condensées de SiO2 doivent figurer dans &lt;species&gt;.</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>Même exigence que C(gr) pour les matériaux carbonés : sans phase condensée, le solveur ne peut pas faire précipiter la silice et B'c sature sur une valeur non physique. Ici il faut les quatre polymorphes (quartz α et β, cristobalite β, liquide) pour couvrir toute la plage de température.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Équilibre thermochimique à la paroi.</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>Identique aux autres matériaux.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>§2 — DONNÉES D'ENTRÉE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>stœchiométrie — ν_Si</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>SiO2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>stœchiométrie — ν_O</t>
-        </is>
-      </c>
-      <c r="C19" s="37" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>masse volumique de la silice [kg/m³]</t>
-        </is>
-      </c>
-      <c r="C20" s="30" t="n">
-        <v>2200</v>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>silice vitreuse — n'entre que dans la récession</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>§3 — CALCUL PAS À PAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>&gt;</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Étape 1 — masse molaire du motif</t>
-        </is>
-      </c>
-      <c r="I23" s="27" t="inlineStr">
-        <is>
-          <t>M = ν_Si·M_Si + ν_O·M_O</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>M(SiO2) [g/mol]</t>
-        </is>
-      </c>
-      <c r="C24" s="63">
-        <f>C18*Constantes!$C$11+C19*Constantes!$C$9</f>
-        <v>60.0835</v>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>attendu 60.08 g/mol</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>&gt;</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>Étape 2 — composition élémentaire, en molaire puis en massique</t>
-        </is>
-      </c>
-      <c r="I25" s="27" t="inlineStr">
-        <is>
-          <t>x_E = ν_E / Σ ν_j ;  y_E = ν_E·M_E / M</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="6" t="inlineStr"/>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Somme</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>ν_E (moles d'atomes par motif)</t>
-        </is>
-      </c>
-      <c r="C27" s="24">
-        <f>C18</f>
-        <v>1.0</v>
-      </c>
-      <c r="D27" s="24">
-        <f>C19</f>
-        <v>2.0</v>
-      </c>
-      <c r="E27" s="24">
-        <f>SUM(C27:D27)</f>
-        <v>3.0</v>
-      </c>
-      <c r="F27" s="15" t="inlineStr"/>
-      <c r="G27" s="15" t="inlineStr"/>
-      <c r="H27" s="15" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>x_E (fraction molaire élémentaire, normalisée)</t>
-        </is>
-      </c>
-      <c r="C28" s="26">
-        <f>C27/$E$27</f>
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D28" s="26">
-        <f>D27/$E$27</f>
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E28" s="24">
-        <f>SUM(C28:D28)</f>
-        <v>1.0</v>
-      </c>
-      <c r="F28" s="15" t="inlineStr"/>
-      <c r="G28" s="15" t="inlineStr"/>
-      <c r="H28" s="15" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>y_E (fraction massique élémentaire)</t>
-        </is>
-      </c>
-      <c r="C29" s="26">
-        <f>C27*Constantes!$C$11/$C$24</f>
-        <v>0.4674411444073664</v>
-      </c>
-      <c r="D29" s="26">
-        <f>D27*Constantes!$C$9/$C$24</f>
-        <v>0.5325588555926336</v>
-      </c>
-      <c r="E29" s="24">
-        <f>SUM(C29:D29)</f>
-        <v>1.0</v>
-      </c>
-      <c r="F29" s="15" t="inlineStr"/>
-      <c r="G29" s="15" t="inlineStr"/>
-      <c r="H29" s="15" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>Attendu : x_Si = 0.3333 / x_O = 0.6667 en molaire, y_Si = 0.4674 / y_O = 0.5326 en masse. Le piège classique est de confondre les deux — le parseur suppose du MOLAIRE par défaut.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>§4 — RÉSULTAT : CE QUI ENTRE DANS LE XML</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Composition élémentaire</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Somme</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>après normalisation par le parseur</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>valeur portée dans le XML (silice)</t>
-        </is>
-      </c>
-      <c r="C34" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="24">
-        <f>SUM(C34:D34)</f>
-        <v>3.0</v>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>x_Si = 1/3, x_O = 2/3</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>C'est l'illustration la plus nette de la règle de normalisation automatique (Composition::componentsFromList) : « Si:1.0, O:2.0 » somme à 3, et le parseur le ramène à 1. On peut donc saisir indifféremment des moles brutes, des pourcentages ou des fractions — c'est le RAPPORT qui compte, et écrire directement Si:0.3333, O:0.6667 donnerait exactement le même mélange.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>§5 — CONTRÔLES ET VALIDATION CROISÉE</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>x_Si + x_O après normalisation</t>
-        </is>
-      </c>
-      <c r="C38" s="60">
-        <f>C28+D28</f>
-        <v>1.0</v>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>doit valoir 1 exactement</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>rapport O/Si</t>
-        </is>
-      </c>
-      <c r="C39" s="63">
-        <f>D27/C27</f>
-        <v>2.0</v>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>doit valoir 2 — la stœchiométrie de la silice</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>Le cas de la silice est aussi le CONTRE-EXEMPLE de référence pour les composites : dès que les constituants ne carbonisent pas vers le même produit (fibres de silice + résine phénolique, par exemple), le char devient multi-élément et il faut pondérer par les MASSES de char de chaque constituant : n_E(char) = Σ_i (m_char,i / M_i)·ν_E,i. Le ratio renfort/résine entre alors dans la table B' — cf. onglet CPh70 §6 pour le cas contraire, et l'onglet Liège-phénolique §5 pour un exemple chiffré de pondération.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>§6 — SENSIBILITÉ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Sans objet : la stœchiométrie SiO2 est exacte, il n'y a ni rendement en char, ni analyse élémentaire, ni motif de résine à choisir. C'est la mise en données la moins incertaine du classeur — l'incertitude est reportée sur la base thermodynamique des quatre phases condensées et sur l'hypothèse d'équilibre à la paroi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>§7 — RÉPONSE MATÉRIAU (n'entre PAS dans le XML)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="35" t="inlineStr">
-        <is>
-          <t>couplage k = B'g / B'c</t>
-        </is>
-      </c>
-      <c r="C46" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>pas de pyrolyse interne — comme le graphite</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="35" t="inlineStr">
-        <is>
-          <t>ρ_char [kg/m³]</t>
-        </is>
-      </c>
-      <c r="C47" s="66">
-        <f>C20</f>
-        <v>2200.0</v>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>la silice fondue est évacuée mécaniquement : la récession réelle dépasse celle donnée par B'c seul</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>§8 — BLOC XML</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="29" t="inlineStr">
-        <is>
-          <t>&lt;mixture thermo_db="NASA-9"&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;species&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        N O NO N2 O2 Si SiO SiO2 Si2 SiN SiO2(a-qz) SiO2(b-qz) SiO2(b-crt) SiO2(L)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;/species&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;element_compositions default="air"&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;composition name="air"&gt;N:0.79, O:0.21&lt;/composition&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        &lt;composition name="silice"&gt;Si:1.0, O:2.0&lt;/composition&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    &lt;/element_compositions&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="29" t="inlineStr">
-        <is>
-          <t>&lt;/mixture&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>bprime_silica -T 300:25:5000 -P &lt;P&gt; -b 0.0 -m silica-air -bl air</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B52:I52"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B53:I53"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B50:I50"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>